--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/19.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/19.xlsx
@@ -426,13 +426,13 @@
         <v>-9.031172149254253</v>
       </c>
       <c r="E2">
-        <v>-13.72075512159871</v>
+        <v>-13.88787619209849</v>
       </c>
       <c r="F2">
-        <v>1.690054080394308</v>
+        <v>-0.9378230484485233</v>
       </c>
       <c r="G2">
-        <v>-17.5647953560746</v>
+        <v>-17.83114743537687</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.86234977576917</v>
       </c>
       <c r="E3">
-        <v>-13.65148786312322</v>
+        <v>-13.99187260367219</v>
       </c>
       <c r="F3">
-        <v>1.574690665676032</v>
+        <v>-0.6669858410010164</v>
       </c>
       <c r="G3">
-        <v>-16.82886953312552</v>
+        <v>-17.57340037024691</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.594484570661796</v>
       </c>
       <c r="E4">
-        <v>-13.10664052905294</v>
+        <v>-14.53779146626428</v>
       </c>
       <c r="F4">
-        <v>2.139965267876804</v>
+        <v>-0.5949427279795435</v>
       </c>
       <c r="G4">
-        <v>-17.20822769205412</v>
+        <v>-17.19217552893566</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.270019984386481</v>
       </c>
       <c r="E5">
-        <v>-13.59809833154255</v>
+        <v>-14.80147885327764</v>
       </c>
       <c r="F5">
-        <v>2.380927404942346</v>
+        <v>-0.4960903323338673</v>
       </c>
       <c r="G5">
-        <v>-16.67488259565248</v>
+        <v>-16.97624867603846</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.900646687111445</v>
       </c>
       <c r="E6">
-        <v>-14.13128344821271</v>
+        <v>-14.28938789692628</v>
       </c>
       <c r="F6">
-        <v>1.803999330118991</v>
+        <v>0.03296473354689857</v>
       </c>
       <c r="G6">
-        <v>-15.73892413287689</v>
+        <v>-16.65959407532692</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.518190200047385</v>
       </c>
       <c r="E7">
-        <v>-15.03188240473383</v>
+        <v>-17.34534570900307</v>
       </c>
       <c r="F7">
-        <v>1.702292380403268</v>
+        <v>-0.4419059921493488</v>
       </c>
       <c r="G7">
-        <v>-16.0506509531727</v>
+        <v>-16.49918731690433</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.136472248186165</v>
       </c>
       <c r="E8">
-        <v>-16.02683816934373</v>
+        <v>-16.45725622499234</v>
       </c>
       <c r="F8">
-        <v>1.806399938852304</v>
+        <v>-0.142643357274777</v>
       </c>
       <c r="G8">
-        <v>-14.08572103007393</v>
+        <v>-16.20467835718691</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.768217393898006</v>
       </c>
       <c r="E9">
-        <v>-15.59919861207143</v>
+        <v>-18.48400673866336</v>
       </c>
       <c r="F9">
-        <v>2.239407461113273</v>
+        <v>0.07001346563710646</v>
       </c>
       <c r="G9">
-        <v>-13.80573564251687</v>
+        <v>-15.52284846753799</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.418880095310285</v>
       </c>
       <c r="E10">
-        <v>-16.99269653541188</v>
+        <v>-18.42015526775545</v>
       </c>
       <c r="F10">
-        <v>2.81924476225526</v>
+        <v>0.4551620612013338</v>
       </c>
       <c r="G10">
-        <v>-13.9965654076597</v>
+        <v>-15.36558896171998</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.083829560202765</v>
       </c>
       <c r="E11">
-        <v>-16.57531956332324</v>
+        <v>-19.28555575829865</v>
       </c>
       <c r="F11">
-        <v>2.499256374962644</v>
+        <v>0.9275418861173631</v>
       </c>
       <c r="G11">
-        <v>-13.44119868063201</v>
+        <v>-15.07220262217674</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.766196649801566</v>
       </c>
       <c r="E12">
-        <v>-18.14488042114582</v>
+        <v>-19.81272702497046</v>
       </c>
       <c r="F12">
-        <v>3.13205617437002</v>
+        <v>0.8018934617259285</v>
       </c>
       <c r="G12">
-        <v>-12.52209649030895</v>
+        <v>-14.25265856609119</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.452405000343243</v>
       </c>
       <c r="E13">
-        <v>-18.25019755392082</v>
+        <v>-19.82002837047951</v>
       </c>
       <c r="F13">
-        <v>2.902946318103733</v>
+        <v>1.356357869320166</v>
       </c>
       <c r="G13">
-        <v>-12.37843896381064</v>
+        <v>-14.03529319292428</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.147139196846445</v>
       </c>
       <c r="E14">
-        <v>-20.15013391299953</v>
+        <v>-20.27482992981619</v>
       </c>
       <c r="F14">
-        <v>3.618589484730282</v>
+        <v>1.714835519616458</v>
       </c>
       <c r="G14">
-        <v>-11.29600728649523</v>
+        <v>-14.00526963012647</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.837095573601607</v>
       </c>
       <c r="E15">
-        <v>-20.86719415465383</v>
+        <v>-21.47999633242096</v>
       </c>
       <c r="F15">
-        <v>3.804002960498895</v>
+        <v>1.639399413713118</v>
       </c>
       <c r="G15">
-        <v>-12.02470917916071</v>
+        <v>-13.87423113760932</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.525348251652997</v>
       </c>
       <c r="E16">
-        <v>-21.01286388866087</v>
+        <v>-21.93763868830381</v>
       </c>
       <c r="F16">
-        <v>4.280885790616543</v>
+        <v>1.906590976220904</v>
       </c>
       <c r="G16">
-        <v>-10.54339619486435</v>
+        <v>-13.40786338832039</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.203099174973399</v>
       </c>
       <c r="E17">
-        <v>-21.56490873795708</v>
+        <v>-22.64536666411122</v>
       </c>
       <c r="F17">
-        <v>3.668639443207428</v>
+        <v>1.991132496615816</v>
       </c>
       <c r="G17">
-        <v>-10.67818632735893</v>
+        <v>-12.73808469570405</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.872089616884827</v>
       </c>
       <c r="E18">
-        <v>-23.17275805098325</v>
+        <v>-24.37626732226941</v>
       </c>
       <c r="F18">
-        <v>4.392171980978239</v>
+        <v>2.146380145044083</v>
       </c>
       <c r="G18">
-        <v>-10.56909636461926</v>
+        <v>-13.15642649286715</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.529710486486531</v>
       </c>
       <c r="E19">
-        <v>-23.59676354834632</v>
+        <v>-24.64395009857726</v>
       </c>
       <c r="F19">
-        <v>4.361131397660536</v>
+        <v>2.744532649461967</v>
       </c>
       <c r="G19">
-        <v>-10.27147931346612</v>
+        <v>-12.61184344637306</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.178697385300191</v>
       </c>
       <c r="E20">
-        <v>-23.6812855520179</v>
+        <v>-25.10435433999113</v>
       </c>
       <c r="F20">
-        <v>4.594956321183559</v>
+        <v>2.326695847815868</v>
       </c>
       <c r="G20">
-        <v>-9.654512067811119</v>
+        <v>-12.54918949230323</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.825056946675621</v>
       </c>
       <c r="E21">
-        <v>-24.25877297389001</v>
+        <v>-26.84114840501925</v>
       </c>
       <c r="F21">
-        <v>4.877164527969294</v>
+        <v>2.795041523480264</v>
       </c>
       <c r="G21">
-        <v>-9.246698098211677</v>
+        <v>-11.89899268949253</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.474538740649162</v>
       </c>
       <c r="E22">
-        <v>-25.31227655854602</v>
+        <v>-26.74778006122579</v>
       </c>
       <c r="F22">
-        <v>5.121907333861214</v>
+        <v>2.840707761661795</v>
       </c>
       <c r="G22">
-        <v>-10.11127227700475</v>
+        <v>-11.42359568003524</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.139183122125697</v>
       </c>
       <c r="E23">
-        <v>-24.91270025019559</v>
+        <v>-27.95182509677285</v>
       </c>
       <c r="F23">
-        <v>4.749523051606723</v>
+        <v>2.404330440806238</v>
       </c>
       <c r="G23">
-        <v>-9.073494775175744</v>
+        <v>-11.13249374200922</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.822561345482106</v>
       </c>
       <c r="E24">
-        <v>-25.11079597075594</v>
+        <v>-27.886478469788</v>
       </c>
       <c r="F24">
-        <v>5.20985013081202</v>
+        <v>2.750223533519199</v>
       </c>
       <c r="G24">
-        <v>-8.442541770746145</v>
+        <v>-10.95889619654003</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.535811249654453</v>
       </c>
       <c r="E25">
-        <v>-27.43348771058895</v>
+        <v>-29.23151879999601</v>
       </c>
       <c r="F25">
-        <v>5.188655522443992</v>
+        <v>2.827438972603753</v>
       </c>
       <c r="G25">
-        <v>-8.891504991218419</v>
+        <v>-11.11141981166975</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.278584101970959</v>
       </c>
       <c r="E26">
-        <v>-26.41330949360337</v>
+        <v>-28.88761005963792</v>
       </c>
       <c r="F26">
-        <v>5.507992812958007</v>
+        <v>2.954487337905918</v>
       </c>
       <c r="G26">
-        <v>-9.266642881515487</v>
+        <v>-10.82756660600096</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.056963071212401</v>
       </c>
       <c r="E27">
-        <v>-26.54512411463078</v>
+        <v>-29.87737223348612</v>
       </c>
       <c r="F27">
-        <v>4.635137110423751</v>
+        <v>2.706624900375056</v>
       </c>
       <c r="G27">
-        <v>-8.634699099513561</v>
+        <v>-10.61505330165663</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.8683715038614854</v>
       </c>
       <c r="E28">
-        <v>-26.55642500264564</v>
+        <v>-30.63128391922562</v>
       </c>
       <c r="F28">
-        <v>4.643225289744685</v>
+        <v>2.464612393442764</v>
       </c>
       <c r="G28">
-        <v>-7.886673780756965</v>
+        <v>-10.04931017025157</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7144820447790011</v>
       </c>
       <c r="E29">
-        <v>-25.72637664689938</v>
+        <v>-30.08943105052054</v>
       </c>
       <c r="F29">
-        <v>4.384816078441379</v>
+        <v>3.002246032146921</v>
       </c>
       <c r="G29">
-        <v>-8.283484767277159</v>
+        <v>-9.58181588467157</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.5930129605876431</v>
       </c>
       <c r="E30">
-        <v>-26.70546299103711</v>
+        <v>-30.62779522171277</v>
       </c>
       <c r="F30">
-        <v>4.377281248545516</v>
+        <v>2.476042206866591</v>
       </c>
       <c r="G30">
-        <v>-8.443535159063064</v>
+        <v>-9.42102404142179</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.5035337791533564</v>
       </c>
       <c r="E31">
-        <v>-27.11778135173211</v>
+        <v>-31.32374469020296</v>
       </c>
       <c r="F31">
-        <v>4.357002814524984</v>
+        <v>2.952885275348904</v>
       </c>
       <c r="G31">
-        <v>-8.137080737469004</v>
+        <v>-8.61441100329602</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4461994943512108</v>
       </c>
       <c r="E32">
-        <v>-26.81970537494917</v>
+        <v>-30.05897762848124</v>
       </c>
       <c r="F32">
-        <v>5.246616389617873</v>
+        <v>2.629160951069663</v>
       </c>
       <c r="G32">
-        <v>-8.280541152750679</v>
+        <v>-8.913696320242883</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.4205188594034895</v>
       </c>
       <c r="E33">
-        <v>-28.09950083184978</v>
+        <v>-30.92236173492623</v>
       </c>
       <c r="F33">
-        <v>5.080831907825997</v>
+        <v>2.536383801956118</v>
       </c>
       <c r="G33">
-        <v>-7.239102081632634</v>
+        <v>-8.768001107591214</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.4296072981764436</v>
       </c>
       <c r="E34">
-        <v>-26.98740374182309</v>
+        <v>-30.87188983430125</v>
       </c>
       <c r="F34">
-        <v>4.640369078939833</v>
+        <v>2.418667823813891</v>
       </c>
       <c r="G34">
-        <v>-8.094053055862867</v>
+        <v>-8.250404022563163</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4720602423031293</v>
       </c>
       <c r="E35">
-        <v>-26.229546505325</v>
+        <v>-30.11790962057489</v>
       </c>
       <c r="F35">
-        <v>4.583743540019264</v>
+        <v>2.639974459145808</v>
       </c>
       <c r="G35">
-        <v>-7.474565136305142</v>
+        <v>-8.217598711403529</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5509309285509533</v>
       </c>
       <c r="E36">
-        <v>-27.78734962188699</v>
+        <v>-29.53877545041249</v>
       </c>
       <c r="F36">
-        <v>4.311465801658289</v>
+        <v>2.812465403430748</v>
       </c>
       <c r="G36">
-        <v>-7.771652206306286</v>
+        <v>-7.706036362497836</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6612219303809497</v>
       </c>
       <c r="E37">
-        <v>-24.51608518151977</v>
+        <v>-29.76284120138699</v>
       </c>
       <c r="F37">
-        <v>5.022567858182691</v>
+        <v>2.829218305784966</v>
       </c>
       <c r="G37">
-        <v>-8.409039390780684</v>
+        <v>-7.574311244153216</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8023630641711456</v>
       </c>
       <c r="E38">
-        <v>-25.54749368192769</v>
+        <v>-30.0097080825348</v>
       </c>
       <c r="F38">
-        <v>4.839926099743844</v>
+        <v>2.822099316325307</v>
       </c>
       <c r="G38">
-        <v>-8.035063281826661</v>
+        <v>-7.730360669853239</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.9672258293946947</v>
       </c>
       <c r="E39">
-        <v>-24.77670749857541</v>
+        <v>-29.14238257854254</v>
       </c>
       <c r="F39">
-        <v>4.832782259262102</v>
+        <v>3.245921900824035</v>
       </c>
       <c r="G39">
-        <v>-8.223039503131409</v>
+        <v>-7.369850781500179</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.152702175497217</v>
       </c>
       <c r="E40">
-        <v>-25.00788354733801</v>
+        <v>-28.96121742394786</v>
       </c>
       <c r="F40">
-        <v>4.883352432468206</v>
+        <v>3.137515115554469</v>
       </c>
       <c r="G40">
-        <v>-8.103780690209355</v>
+        <v>-7.616179755160899</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.352348739551559</v>
       </c>
       <c r="E41">
-        <v>-24.69048683147196</v>
+        <v>-28.9553697024025</v>
       </c>
       <c r="F41">
-        <v>4.958780254697518</v>
+        <v>3.344739505038793</v>
       </c>
       <c r="G41">
-        <v>-8.23479046453601</v>
+        <v>-7.559529208278332</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.561652712807507</v>
       </c>
       <c r="E42">
-        <v>-24.00878287782593</v>
+        <v>-28.95348829767235</v>
       </c>
       <c r="F42">
-        <v>4.740710879175743</v>
+        <v>3.334018774111762</v>
       </c>
       <c r="G42">
-        <v>-7.779886494746658</v>
+        <v>-8.030185105558166</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.776737485988297</v>
       </c>
       <c r="E43">
-        <v>-23.99515203825785</v>
+        <v>-28.04203699995945</v>
       </c>
       <c r="F43">
-        <v>4.877088318168236</v>
+        <v>3.339305414876428</v>
       </c>
       <c r="G43">
-        <v>-8.096449719397508</v>
+        <v>-8.157750002396847</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.993129690267677</v>
       </c>
       <c r="E44">
-        <v>-23.56467168443937</v>
+        <v>-28.16509665151412</v>
       </c>
       <c r="F44">
-        <v>5.170461260808904</v>
+        <v>3.577880197087103</v>
       </c>
       <c r="G44">
-        <v>-8.092905633615072</v>
+        <v>-8.161207933607777</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.209729824387547</v>
       </c>
       <c r="E45">
-        <v>-23.42695119690805</v>
+        <v>-28.12570759530945</v>
       </c>
       <c r="F45">
-        <v>4.975142167637614</v>
+        <v>3.572772483681441</v>
       </c>
       <c r="G45">
-        <v>-7.679158746932325</v>
+        <v>-7.901434930675119</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.421719373685435</v>
       </c>
       <c r="E46">
-        <v>-23.01129780751921</v>
+        <v>-26.76011925207185</v>
       </c>
       <c r="F46">
-        <v>4.826036035133702</v>
+        <v>3.670983722957351</v>
       </c>
       <c r="G46">
-        <v>-8.154935619727627</v>
+        <v>-8.661084589723647</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.630123912204563</v>
       </c>
       <c r="E47">
-        <v>-21.52468488627611</v>
+        <v>-26.09658975118327</v>
       </c>
       <c r="F47">
-        <v>5.115732683240746</v>
+        <v>3.65883985683231</v>
       </c>
       <c r="G47">
-        <v>-7.304749254376177</v>
+        <v>-8.847455203104861</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.829586490420944</v>
       </c>
       <c r="E48">
-        <v>-22.33262154492898</v>
+        <v>-26.19485057791739</v>
       </c>
       <c r="F48">
-        <v>4.930890780980064</v>
+        <v>3.303314507959596</v>
       </c>
       <c r="G48">
-        <v>-8.173290459575449</v>
+        <v>-9.376039606744612</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.022854059228973</v>
       </c>
       <c r="E49">
-        <v>-21.18481514393142</v>
+        <v>-25.88613407372023</v>
       </c>
       <c r="F49">
-        <v>4.896248456194989</v>
+        <v>3.672852519818066</v>
       </c>
       <c r="G49">
-        <v>-8.601378166297183</v>
+        <v>-8.661134193870879</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.205191223736296</v>
       </c>
       <c r="E50">
-        <v>-21.04396313506118</v>
+        <v>-25.81934628240566</v>
       </c>
       <c r="F50">
-        <v>5.372167066655778</v>
+        <v>3.513381854370328</v>
       </c>
       <c r="G50">
-        <v>-8.352448891023712</v>
+        <v>-9.08282949246127</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.378817049053213</v>
       </c>
       <c r="E51">
-        <v>-19.87029468714391</v>
+        <v>-25.31553682943601</v>
       </c>
       <c r="F51">
-        <v>5.242734659968355</v>
+        <v>3.561771764572264</v>
       </c>
       <c r="G51">
-        <v>-8.595601893889343</v>
+        <v>-9.756978571523133</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.540389654334989</v>
       </c>
       <c r="E52">
-        <v>-19.66614358447196</v>
+        <v>-24.29633877032309</v>
       </c>
       <c r="F52">
-        <v>5.202297076833294</v>
+        <v>3.565244280724799</v>
       </c>
       <c r="G52">
-        <v>-9.097940482154634</v>
+        <v>-9.445935766310193</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.689743963699099</v>
       </c>
       <c r="E53">
-        <v>-21.55655662998285</v>
+        <v>-24.18828882449635</v>
       </c>
       <c r="F53">
-        <v>4.841610999041139</v>
+        <v>3.508540875268368</v>
       </c>
       <c r="G53">
-        <v>-8.916466320254054</v>
+        <v>-9.664355880291913</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.825690110434169</v>
       </c>
       <c r="E54">
-        <v>-18.21523997419974</v>
+        <v>-23.76789662098588</v>
       </c>
       <c r="F54">
-        <v>4.703873380773248</v>
+        <v>3.716298733360095</v>
       </c>
       <c r="G54">
-        <v>-9.528949612073822</v>
+        <v>-9.619738255229786</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.946425039103646</v>
       </c>
       <c r="E55">
-        <v>-18.82406337551768</v>
+        <v>-23.46572557783665</v>
       </c>
       <c r="F55">
-        <v>4.395836678368224</v>
+        <v>3.691444397806498</v>
       </c>
       <c r="G55">
-        <v>-9.967080853237567</v>
+        <v>-10.11822599522318</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.054966345474983</v>
       </c>
       <c r="E56">
-        <v>-19.41838791610064</v>
+        <v>-21.82798975611702</v>
       </c>
       <c r="F56">
-        <v>4.735835108642864</v>
+        <v>3.6923622288888</v>
       </c>
       <c r="G56">
-        <v>-9.97133375617649</v>
+        <v>-10.11707074074162</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.148687028738108</v>
       </c>
       <c r="E57">
-        <v>-19.32071684537465</v>
+        <v>-22.58997943788331</v>
       </c>
       <c r="F57">
-        <v>4.398492424261599</v>
+        <v>3.791060548197556</v>
       </c>
       <c r="G57">
-        <v>-10.33462539289138</v>
+        <v>-10.04305221546667</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.235156939186285</v>
       </c>
       <c r="E58">
-        <v>-18.20624827168148</v>
+        <v>-22.26142719639877</v>
       </c>
       <c r="F58">
-        <v>4.632897204966581</v>
+        <v>4.058691145428826</v>
       </c>
       <c r="G58">
-        <v>-9.783867935439305</v>
+        <v>-10.28781213162813</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.311492900544126</v>
       </c>
       <c r="E59">
-        <v>-18.18374201951224</v>
+        <v>-21.58143021260724</v>
       </c>
       <c r="F59">
-        <v>4.569896550514068</v>
+        <v>3.957002419795964</v>
       </c>
       <c r="G59">
-        <v>-9.81177548974601</v>
+        <v>-10.0960398876879</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.386975570829895</v>
       </c>
       <c r="E60">
-        <v>-18.94935330155378</v>
+        <v>-21.89211533897237</v>
       </c>
       <c r="F60">
-        <v>4.991997787549778</v>
+        <v>3.975703642281565</v>
       </c>
       <c r="G60">
-        <v>-10.19664101438957</v>
+        <v>-10.70357451313522</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.457865560302531</v>
       </c>
       <c r="E61">
-        <v>-17.68097917579644</v>
+        <v>-21.47609646698694</v>
       </c>
       <c r="F61">
-        <v>4.82749396176263</v>
+        <v>4.199755487186359</v>
       </c>
       <c r="G61">
-        <v>-9.786327256844134</v>
+        <v>-10.58606489908921</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.531072629295537</v>
       </c>
       <c r="E62">
-        <v>-16.52440949890349</v>
+        <v>-21.19086221962037</v>
       </c>
       <c r="F62">
-        <v>4.558450169742184</v>
+        <v>4.038460756717656</v>
       </c>
       <c r="G62">
-        <v>-10.05746352560961</v>
+        <v>-11.0711268850228</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.604099244792551</v>
       </c>
       <c r="E63">
-        <v>-15.82725975234042</v>
+        <v>-20.58123724851674</v>
       </c>
       <c r="F63">
-        <v>5.007703633506857</v>
+        <v>4.003379397209097</v>
       </c>
       <c r="G63">
-        <v>-10.83310530065101</v>
+        <v>-11.0330543966506</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.679367310044374</v>
       </c>
       <c r="E64">
-        <v>-16.36223074988026</v>
+        <v>-20.86529198386706</v>
       </c>
       <c r="F64">
-        <v>4.367996906694938</v>
+        <v>3.829857963875073</v>
       </c>
       <c r="G64">
-        <v>-11.21733249824204</v>
+        <v>-11.42564511453926</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.756416108784098</v>
       </c>
       <c r="E65">
-        <v>-15.32683931981183</v>
+        <v>-19.97168703521695</v>
       </c>
       <c r="F65">
-        <v>5.080671204549854</v>
+        <v>3.906453784142332</v>
       </c>
       <c r="G65">
-        <v>-10.31511660393429</v>
+        <v>-11.2484538791404</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.833413200427607</v>
       </c>
       <c r="E66">
-        <v>-16.22147426487049</v>
+        <v>-20.45561921878597</v>
       </c>
       <c r="F66">
-        <v>4.584455935985671</v>
+        <v>4.345211832913535</v>
       </c>
       <c r="G66">
-        <v>-10.23550586374517</v>
+        <v>-12.16746730414737</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.913054102199056</v>
       </c>
       <c r="E67">
-        <v>-16.69177976208276</v>
+        <v>-21.34350934865311</v>
       </c>
       <c r="F67">
-        <v>4.974088484301252</v>
+        <v>3.947564001608466</v>
       </c>
       <c r="G67">
-        <v>-10.55548133157661</v>
+        <v>-11.73246765112067</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.989776537007534</v>
       </c>
       <c r="E68">
-        <v>-16.17152359226678</v>
+        <v>-20.58390361018727</v>
       </c>
       <c r="F68">
-        <v>4.114412107145538</v>
+        <v>4.045511820050286</v>
       </c>
       <c r="G68">
-        <v>-10.82180338731608</v>
+        <v>-11.9641320724131</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.069497921961005</v>
       </c>
       <c r="E69">
-        <v>-14.76497627894372</v>
+        <v>-20.69969098871217</v>
       </c>
       <c r="F69">
-        <v>4.59543014733796</v>
+        <v>4.539121044765261</v>
       </c>
       <c r="G69">
-        <v>-11.28941646177497</v>
+        <v>-11.90053433417358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.143960251674748</v>
       </c>
       <c r="E70">
-        <v>-16.93492536588352</v>
+        <v>-19.75950362184278</v>
       </c>
       <c r="F70">
-        <v>5.026413139666486</v>
+        <v>4.487826878449109</v>
       </c>
       <c r="G70">
-        <v>-10.50663560564918</v>
+        <v>-12.26072701705882</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.221306641914201</v>
       </c>
       <c r="E71">
-        <v>-16.14147510833165</v>
+        <v>-19.96381254654507</v>
       </c>
       <c r="F71">
-        <v>4.916387724491851</v>
+        <v>4.439142069451777</v>
       </c>
       <c r="G71">
-        <v>-10.6506703847409</v>
+        <v>-12.7739680747366</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.293877287092366</v>
       </c>
       <c r="E72">
-        <v>-18.17735022728333</v>
+        <v>-19.60252469339824</v>
       </c>
       <c r="F72">
-        <v>5.134266575510982</v>
+        <v>3.990266341222781</v>
       </c>
       <c r="G72">
-        <v>-10.66228819817135</v>
+        <v>-12.81272457819168</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.369305541874168</v>
       </c>
       <c r="E73">
-        <v>-18.04393246668453</v>
+        <v>-20.25040904722619</v>
       </c>
       <c r="F73">
-        <v>4.416472967106766</v>
+        <v>4.519382706291354</v>
       </c>
       <c r="G73">
-        <v>-10.51592071878747</v>
+        <v>-12.76928831505703</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.442988996971949</v>
       </c>
       <c r="E74">
-        <v>-16.94839838342126</v>
+        <v>-19.53658415719394</v>
       </c>
       <c r="F74">
-        <v>4.58800300520446</v>
+        <v>4.424156903135134</v>
       </c>
       <c r="G74">
-        <v>-11.35655959116922</v>
+        <v>-12.81878803250454</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.51846149862394</v>
       </c>
       <c r="E75">
-        <v>-16.85268347522926</v>
+        <v>-19.96005804350743</v>
       </c>
       <c r="F75">
-        <v>4.340751902816863</v>
+        <v>4.527371481523952</v>
       </c>
       <c r="G75">
-        <v>-9.823311064721844</v>
+        <v>-13.03933720870031</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.595339710814184</v>
       </c>
       <c r="E76">
-        <v>-18.55584483494892</v>
+        <v>-20.35462142578879</v>
       </c>
       <c r="F76">
-        <v>4.678495517021083</v>
+        <v>4.53874496596439</v>
       </c>
       <c r="G76">
-        <v>-11.27249883682455</v>
+        <v>-13.37219017422741</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.67336452682272</v>
       </c>
       <c r="E77">
-        <v>-18.39487882363255</v>
+        <v>-21.11349204585014</v>
       </c>
       <c r="F77">
-        <v>4.128007272960282</v>
+        <v>4.514599712907589</v>
       </c>
       <c r="G77">
-        <v>-10.62678337710451</v>
+        <v>-12.61198834269786</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.757148973200537</v>
       </c>
       <c r="E78">
-        <v>-18.05048623415511</v>
+        <v>-21.28882816835042</v>
       </c>
       <c r="F78">
-        <v>4.325276342997762</v>
+        <v>4.209255204561663</v>
       </c>
       <c r="G78">
-        <v>-10.50738097322994</v>
+        <v>-12.46689360130215</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.842319781121344</v>
       </c>
       <c r="E79">
-        <v>-17.91681928087683</v>
+        <v>-20.76777458196008</v>
       </c>
       <c r="F79">
-        <v>4.410846695706951</v>
+        <v>4.53979864930075</v>
       </c>
       <c r="G79">
-        <v>-9.515764046516404</v>
+        <v>-12.84157591666807</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.937147003797118</v>
       </c>
       <c r="E80">
-        <v>-18.8974007810915</v>
+        <v>-21.41007286655614</v>
       </c>
       <c r="F80">
-        <v>4.595241279570121</v>
+        <v>4.133423139039786</v>
       </c>
       <c r="G80">
-        <v>-10.61025866921505</v>
+        <v>-12.49525673054001</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.032851846140809</v>
       </c>
       <c r="E81">
-        <v>-19.47381252123048</v>
+        <v>-21.45932579965729</v>
       </c>
       <c r="F81">
-        <v>5.247302277827392</v>
+        <v>4.444774967790813</v>
       </c>
       <c r="G81">
-        <v>-10.49883600618323</v>
+        <v>-12.66453740982779</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.138622823485431</v>
       </c>
       <c r="E82">
-        <v>-20.52378172304906</v>
+        <v>-22.9057273288534</v>
       </c>
       <c r="F82">
-        <v>4.340471914634716</v>
+        <v>4.322504625667995</v>
       </c>
       <c r="G82">
-        <v>-10.02186863385437</v>
+        <v>-12.42948815817298</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.243392753388293</v>
       </c>
       <c r="E83">
-        <v>-20.34184199454229</v>
+        <v>-23.82011494697295</v>
       </c>
       <c r="F83">
-        <v>4.354588951913226</v>
+        <v>4.919499072456765</v>
       </c>
       <c r="G83">
-        <v>-9.611005314572513</v>
+        <v>-12.63726687720132</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.353065142719782</v>
       </c>
       <c r="E84">
-        <v>-22.41250441155074</v>
+        <v>-24.62727080189675</v>
       </c>
       <c r="F84">
-        <v>4.834768684294015</v>
+        <v>4.163489562291796</v>
       </c>
       <c r="G84">
-        <v>-9.510744890039989</v>
+        <v>-12.00576561640759</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.458217911584605</v>
       </c>
       <c r="E85">
-        <v>-21.98616896263443</v>
+        <v>-25.8511017361953</v>
       </c>
       <c r="F85">
-        <v>4.502222247174959</v>
+        <v>4.574136134881596</v>
       </c>
       <c r="G85">
-        <v>-10.20094091073113</v>
+        <v>-12.53102132069367</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.558985114710518</v>
       </c>
       <c r="E86">
-        <v>-24.25405492582501</v>
+        <v>-26.23207996423315</v>
       </c>
       <c r="F86">
-        <v>4.747001501232602</v>
+        <v>5.19281227007124</v>
       </c>
       <c r="G86">
-        <v>-9.598327538838065</v>
+        <v>-11.96228627598719</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.649968258354042</v>
       </c>
       <c r="E87">
-        <v>-25.14882277364607</v>
+        <v>-27.63997291802545</v>
       </c>
       <c r="F87">
-        <v>4.84128296554963</v>
+        <v>4.539013357002896</v>
       </c>
       <c r="G87">
-        <v>-10.05472746527813</v>
+        <v>-12.02891378332469</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.726322895511878</v>
       </c>
       <c r="E88">
-        <v>-27.24563796236696</v>
+        <v>-28.47834846247799</v>
       </c>
       <c r="F88">
-        <v>4.952421706513629</v>
+        <v>5.274721238860055</v>
       </c>
       <c r="G88">
-        <v>-9.455429739015775</v>
+        <v>-11.86065651591662</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.78673712729965</v>
       </c>
       <c r="E89">
-        <v>-27.1404454259317</v>
+        <v>-29.71628785564699</v>
       </c>
       <c r="F89">
-        <v>4.525651790795741</v>
+        <v>5.20343194017513</v>
       </c>
       <c r="G89">
-        <v>-9.382395464451678</v>
+        <v>-12.06855924531304</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.821284099247956</v>
       </c>
       <c r="E90">
-        <v>-30.89447499748567</v>
+        <v>-30.93224845448499</v>
       </c>
       <c r="F90">
-        <v>5.002751653172921</v>
+        <v>5.390455762174785</v>
       </c>
       <c r="G90">
-        <v>-8.605922167258015</v>
+        <v>-11.44539800811562</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.831095832035581</v>
       </c>
       <c r="E91">
-        <v>-30.54948434557746</v>
+        <v>-32.52353891395907</v>
       </c>
       <c r="F91">
-        <v>4.653147474495418</v>
+        <v>5.160270685019664</v>
       </c>
       <c r="G91">
-        <v>-8.62216360935933</v>
+        <v>-10.76521680367599</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.801445114029024</v>
       </c>
       <c r="E92">
-        <v>-32.48477699266444</v>
+        <v>-34.30733279494461</v>
       </c>
       <c r="F92">
-        <v>4.292569084465627</v>
+        <v>5.190956727088969</v>
       </c>
       <c r="G92">
-        <v>-9.237448230125363</v>
+        <v>-11.21062549538746</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.735092506113225</v>
       </c>
       <c r="E93">
-        <v>-34.46353507287142</v>
+        <v>-36.03653478967095</v>
       </c>
       <c r="F93">
-        <v>5.127091257067932</v>
+        <v>5.73189058152588</v>
       </c>
       <c r="G93">
-        <v>-8.739124967041205</v>
+        <v>-11.31802761174898</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.618684090297961</v>
       </c>
       <c r="E94">
-        <v>-36.20712794483828</v>
+        <v>-38.70522018194712</v>
       </c>
       <c r="F94">
-        <v>4.66299841964951</v>
+        <v>5.571681012354844</v>
       </c>
       <c r="G94">
-        <v>-9.025445326348599</v>
+        <v>-11.13578197482172</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.458480049671151</v>
       </c>
       <c r="E95">
-        <v>-37.42456916351359</v>
+        <v>-40.70751658733756</v>
       </c>
       <c r="F95">
-        <v>5.032932391126518</v>
+        <v>5.341643384597422</v>
       </c>
       <c r="G95">
-        <v>-8.154185030657683</v>
+        <v>-10.91612175715923</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.249687693220419</v>
       </c>
       <c r="E96">
-        <v>-41.61864808777844</v>
+        <v>-42.08649073067507</v>
       </c>
       <c r="F96">
-        <v>4.645032787417594</v>
+        <v>5.791783201483089</v>
       </c>
       <c r="G96">
-        <v>-8.169993089156874</v>
+        <v>-10.87846959866619</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.003889943067851</v>
       </c>
       <c r="E97">
-        <v>-42.91075366304585</v>
+        <v>-45.46689637314464</v>
       </c>
       <c r="F97">
-        <v>4.223133672028166</v>
+        <v>5.63881024994291</v>
       </c>
       <c r="G97">
-        <v>-8.038416783253947</v>
+        <v>-11.13639549980063</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.727322777909412</v>
       </c>
       <c r="E98">
-        <v>-45.37905699192735</v>
+        <v>-47.06191122487427</v>
       </c>
       <c r="F98">
-        <v>4.211104120604713</v>
+        <v>5.615132196101289</v>
       </c>
       <c r="G98">
-        <v>-8.752088619308379</v>
+        <v>-10.85502511223799</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.438322419336322</v>
       </c>
       <c r="E99">
-        <v>-48.37001081695359</v>
+        <v>-49.31435035684497</v>
       </c>
       <c r="F99">
-        <v>4.671633321456292</v>
+        <v>5.638545172374014</v>
       </c>
       <c r="G99">
-        <v>-8.163937467077787</v>
+        <v>-10.87229388233591</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.151216004038536</v>
       </c>
       <c r="E100">
-        <v>-49.56384518245856</v>
+        <v>-51.6279829044757</v>
       </c>
       <c r="F100">
-        <v>4.346434503200068</v>
+        <v>5.510072015139034</v>
       </c>
       <c r="G100">
-        <v>-8.08206843281736</v>
+        <v>-10.21180421897475</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.891169441701849</v>
       </c>
       <c r="E101">
-        <v>-52.63800963468057</v>
+        <v>-53.50542339441348</v>
       </c>
       <c r="F101">
-        <v>3.405763674868227</v>
+        <v>5.920287836679377</v>
       </c>
       <c r="G101">
-        <v>-8.835490160643788</v>
+        <v>-10.19387493049528</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.669034453756861</v>
       </c>
       <c r="E102">
-        <v>-53.61288981404908</v>
+        <v>-55.50395076052664</v>
       </c>
       <c r="F102">
-        <v>3.630897367601077</v>
+        <v>5.783297405808812</v>
       </c>
       <c r="G102">
-        <v>-8.488430828424143</v>
+        <v>-10.59301078507386</v>
       </c>
     </row>
   </sheetData>
